--- a/SysCall-BackEnd/Tabela de Instâncias/Instancias - SysCall.xlsx
+++ b/SysCall-BackEnd/Tabela de Instâncias/Instancias - SysCall.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsilva\Desktop\Syscall\SysCall-BackEnd\Tabela de Instâncias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rapha\Desktop\SysCall\SysCall-BackEnd\SysCall-BackEnd\Tabela de Instâncias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06A54C04-8300-45D4-A709-1CBA4A5B18D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0472-E8DE-47A3-AA00-8C830A307724}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -497,21 +496,12 @@
     <t>date</t>
   </si>
   <si>
-    <t>schema_auth_saved_user</t>
-  </si>
-  <si>
-    <t>schema_auth_owner_user</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>schema_auth_requester_user</t>
-  </si>
-  <si>
     <t>AC</t>
   </si>
   <si>
@@ -614,17 +604,26 @@
     <t xml:space="preserve">        status</t>
   </si>
   <si>
-    <t xml:space="preserve">        schema_auth_recived_user</t>
-  </si>
-  <si>
     <t>public.user</t>
+  </si>
+  <si>
+    <t>saved_user</t>
+  </si>
+  <si>
+    <t>owner_user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    recived_user</t>
+  </si>
+  <si>
+    <t>requester_user</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -644,6 +643,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -727,7 +734,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -760,6 +767,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1105,22 +1118,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F702C4-BAA8-415A-A39B-B030BE0B18FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="D36:K147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.69921875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:11">
       <c r="D36" s="11" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
@@ -1130,9 +1143,9 @@
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
     </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:11">
       <c r="D37" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>1</v>
@@ -1147,7 +1160,7 @@
         <v>4</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>5</v>
@@ -1156,7 +1169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:11">
       <c r="D38" s="7">
         <v>1</v>
       </c>
@@ -1173,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>9</v>
@@ -1182,7 +1195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:11">
       <c r="D39" s="7">
         <v>2</v>
       </c>
@@ -1199,7 +1212,7 @@
         <v>13</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>9</v>
@@ -1208,7 +1221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:11">
       <c r="D40" s="7">
         <v>3</v>
       </c>
@@ -1225,7 +1238,7 @@
         <v>16</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>9</v>
@@ -1234,7 +1247,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:11">
       <c r="D41" s="7">
         <v>4</v>
       </c>
@@ -1251,7 +1264,7 @@
         <v>19</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>9</v>
@@ -1260,7 +1273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:11">
       <c r="D42" s="7">
         <v>5</v>
       </c>
@@ -1277,7 +1290,7 @@
         <v>21</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>9</v>
@@ -1286,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:11">
       <c r="D43" s="7">
         <v>6</v>
       </c>
@@ -1303,7 +1316,7 @@
         <v>24</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>9</v>
@@ -1312,7 +1325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:11">
       <c r="D44" s="7">
         <v>7</v>
       </c>
@@ -1329,7 +1342,7 @@
         <v>27</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>9</v>
@@ -1338,7 +1351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:11">
       <c r="D45" s="7">
         <v>8</v>
       </c>
@@ -1355,7 +1368,7 @@
         <v>30</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>9</v>
@@ -1364,7 +1377,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:11">
       <c r="D46" s="7">
         <v>9</v>
       </c>
@@ -1381,7 +1394,7 @@
         <v>33</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>9</v>
@@ -1390,7 +1403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:11">
       <c r="D47" s="7">
         <v>10</v>
       </c>
@@ -1407,7 +1420,7 @@
         <v>36</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>9</v>
@@ -1416,7 +1429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:11">
       <c r="D48" s="7">
         <v>11</v>
       </c>
@@ -1433,7 +1446,7 @@
         <v>39</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>9</v>
@@ -1442,7 +1455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:11">
       <c r="D49" s="7">
         <v>12</v>
       </c>
@@ -1459,7 +1472,7 @@
         <v>42</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>9</v>
@@ -1468,7 +1481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:11">
       <c r="D50" s="7">
         <v>13</v>
       </c>
@@ -1485,7 +1498,7 @@
         <v>45</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>9</v>
@@ -1494,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:11">
       <c r="D51" s="7">
         <v>14</v>
       </c>
@@ -1511,7 +1524,7 @@
         <v>48</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>9</v>
@@ -1520,7 +1533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:11">
       <c r="D52" s="7">
         <v>15</v>
       </c>
@@ -1537,7 +1550,7 @@
         <v>51</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>9</v>
@@ -1546,7 +1559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:11">
       <c r="D53" s="7">
         <v>16</v>
       </c>
@@ -1563,7 +1576,7 @@
         <v>54</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>9</v>
@@ -1572,7 +1585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:11">
       <c r="D54" s="7">
         <v>17</v>
       </c>
@@ -1589,7 +1602,7 @@
         <v>57</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>9</v>
@@ -1598,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:11">
       <c r="D55" s="7">
         <v>18</v>
       </c>
@@ -1615,7 +1628,7 @@
         <v>60</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>9</v>
@@ -1624,7 +1637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:11">
       <c r="D56" s="7">
         <v>19</v>
       </c>
@@ -1641,7 +1654,7 @@
         <v>63</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>9</v>
@@ -1650,7 +1663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:11">
       <c r="D57" s="7">
         <v>20</v>
       </c>
@@ -1667,7 +1680,7 @@
         <v>65</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>9</v>
@@ -1676,7 +1689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:11">
       <c r="D58" s="7">
         <v>21</v>
       </c>
@@ -1693,7 +1706,7 @@
         <v>67</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>9</v>
@@ -1702,7 +1715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:11">
       <c r="D59" s="7">
         <v>22</v>
       </c>
@@ -1719,7 +1732,7 @@
         <v>69</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>9</v>
@@ -1728,7 +1741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:11">
       <c r="D60" s="7">
         <v>23</v>
       </c>
@@ -1745,7 +1758,7 @@
         <v>71</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>9</v>
@@ -1754,7 +1767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:11">
       <c r="D61" s="7">
         <v>24</v>
       </c>
@@ -1771,7 +1784,7 @@
         <v>73</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>9</v>
@@ -1780,7 +1793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:11">
       <c r="D62" s="7">
         <v>25</v>
       </c>
@@ -1797,7 +1810,7 @@
         <v>75</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>9</v>
@@ -1806,7 +1819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:11">
       <c r="D63" s="7">
         <v>26</v>
       </c>
@@ -1823,7 +1836,7 @@
         <v>77</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>9</v>
@@ -1832,7 +1845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:11">
       <c r="D64" s="7">
         <v>27</v>
       </c>
@@ -1849,7 +1862,7 @@
         <v>79</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>9</v>
@@ -1858,7 +1871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:11">
       <c r="D65" s="7">
         <v>28</v>
       </c>
@@ -1875,7 +1888,7 @@
         <v>81</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>9</v>
@@ -1884,7 +1897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:11">
       <c r="D66" s="7">
         <v>29</v>
       </c>
@@ -1901,7 +1914,7 @@
         <v>83</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>9</v>
@@ -1910,7 +1923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:11">
       <c r="D67" s="7">
         <v>30</v>
       </c>
@@ -1927,7 +1940,7 @@
         <v>85</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>9</v>
@@ -1936,7 +1949,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:11">
       <c r="D68" s="7">
         <v>31</v>
       </c>
@@ -1953,7 +1966,7 @@
         <v>87</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>9</v>
@@ -1962,7 +1975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:11">
       <c r="D69" s="7">
         <v>32</v>
       </c>
@@ -1979,7 +1992,7 @@
         <v>89</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>9</v>
@@ -1988,7 +2001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:11">
       <c r="D70" s="7">
         <v>33</v>
       </c>
@@ -2005,7 +2018,7 @@
         <v>91</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>9</v>
@@ -2014,7 +2027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:11">
       <c r="D71" s="7">
         <v>34</v>
       </c>
@@ -2031,7 +2044,7 @@
         <v>93</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>9</v>
@@ -2040,33 +2053,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:11">
       <c r="D72" s="7">
         <v>35</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="12">
         <v>55923458901</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="I72" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="I72" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K72" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="4:11">
       <c r="D73" s="7">
         <v>36</v>
       </c>
@@ -2083,7 +2096,7 @@
         <v>97</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>9</v>
@@ -2092,7 +2105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:11">
       <c r="D74" s="7">
         <v>37</v>
       </c>
@@ -2109,7 +2122,7 @@
         <v>99</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>9</v>
@@ -2118,7 +2131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:11">
       <c r="D75" s="7">
         <v>38</v>
       </c>
@@ -2135,7 +2148,7 @@
         <v>101</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>9</v>
@@ -2144,7 +2157,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:11">
       <c r="D76" s="7">
         <v>39</v>
       </c>
@@ -2161,7 +2174,7 @@
         <v>103</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>9</v>
@@ -2170,7 +2183,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:11">
       <c r="D77" s="7">
         <v>40</v>
       </c>
@@ -2187,7 +2200,7 @@
         <v>105</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>9</v>
@@ -2196,7 +2209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:11">
       <c r="D78" s="7">
         <v>41</v>
       </c>
@@ -2213,7 +2226,7 @@
         <v>107</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>9</v>
@@ -2222,7 +2235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:11">
       <c r="D79" s="7">
         <v>42</v>
       </c>
@@ -2239,7 +2252,7 @@
         <v>108</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>9</v>
@@ -2248,7 +2261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:11">
       <c r="D80" s="7">
         <v>43</v>
       </c>
@@ -2265,7 +2278,7 @@
         <v>109</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>9</v>
@@ -2274,7 +2287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:11">
       <c r="D81" s="7">
         <v>44</v>
       </c>
@@ -2291,7 +2304,7 @@
         <v>110</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>9</v>
@@ -2300,7 +2313,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:11">
       <c r="D82" s="7">
         <v>45</v>
       </c>
@@ -2317,7 +2330,7 @@
         <v>111</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>9</v>
@@ -2326,7 +2339,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:11">
       <c r="D83" s="7">
         <v>46</v>
       </c>
@@ -2343,7 +2356,7 @@
         <v>112</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>9</v>
@@ -2352,7 +2365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:11">
       <c r="D84" s="7">
         <v>47</v>
       </c>
@@ -2369,7 +2382,7 @@
         <v>113</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>9</v>
@@ -2378,7 +2391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:11">
       <c r="D85" s="7">
         <v>48</v>
       </c>
@@ -2395,7 +2408,7 @@
         <v>114</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>9</v>
@@ -2404,7 +2417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:11">
       <c r="D86" s="7">
         <v>49</v>
       </c>
@@ -2421,7 +2434,7 @@
         <v>115</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>9</v>
@@ -2430,7 +2443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:11">
       <c r="D87" s="7">
         <v>50</v>
       </c>
@@ -2447,7 +2460,7 @@
         <v>116</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>9</v>
@@ -2456,7 +2469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:11">
       <c r="D88" s="7">
         <v>51</v>
       </c>
@@ -2473,7 +2486,7 @@
         <v>117</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>9</v>
@@ -2482,7 +2495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:11">
       <c r="D89" s="7">
         <v>52</v>
       </c>
@@ -2499,7 +2512,7 @@
         <v>118</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>9</v>
@@ -2508,7 +2521,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:11">
       <c r="D90" s="7">
         <v>53</v>
       </c>
@@ -2525,7 +2538,7 @@
         <v>119</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J90" s="3" t="s">
         <v>9</v>
@@ -2534,7 +2547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:11">
       <c r="D91" s="7">
         <v>54</v>
       </c>
@@ -2551,7 +2564,7 @@
         <v>120</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>9</v>
@@ -2560,7 +2573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:11">
       <c r="D92" s="7">
         <v>55</v>
       </c>
@@ -2577,7 +2590,7 @@
         <v>121</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>9</v>
@@ -2586,7 +2599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:11">
       <c r="D93" s="7">
         <v>56</v>
       </c>
@@ -2603,7 +2616,7 @@
         <v>122</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>9</v>
@@ -2612,7 +2625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:11">
       <c r="D94" s="7">
         <v>57</v>
       </c>
@@ -2629,7 +2642,7 @@
         <v>123</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>9</v>
@@ -2638,7 +2651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:11">
       <c r="D95" s="7">
         <v>58</v>
       </c>
@@ -2655,7 +2668,7 @@
         <v>124</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>9</v>
@@ -2664,7 +2677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:11">
       <c r="D96" s="7">
         <v>59</v>
       </c>
@@ -2681,7 +2694,7 @@
         <v>125</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>9</v>
@@ -2690,7 +2703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:11">
       <c r="D97" s="7">
         <v>60</v>
       </c>
@@ -2707,7 +2720,7 @@
         <v>126</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J97" s="3" t="s">
         <v>9</v>
@@ -2716,7 +2729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:11">
       <c r="D98" s="7">
         <v>61</v>
       </c>
@@ -2733,7 +2746,7 @@
         <v>127</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J98" s="3" t="s">
         <v>9</v>
@@ -2742,7 +2755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:11">
       <c r="D99" s="7">
         <v>62</v>
       </c>
@@ -2759,7 +2772,7 @@
         <v>128</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>9</v>
@@ -2768,7 +2781,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:11">
       <c r="D100" s="7">
         <v>63</v>
       </c>
@@ -2785,7 +2798,7 @@
         <v>129</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>9</v>
@@ -2794,7 +2807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:11">
       <c r="D101" s="7">
         <v>64</v>
       </c>
@@ -2811,7 +2824,7 @@
         <v>130</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>9</v>
@@ -2820,7 +2833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:11">
       <c r="D102" s="7">
         <v>65</v>
       </c>
@@ -2837,7 +2850,7 @@
         <v>131</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>9</v>
@@ -2846,7 +2859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:11">
       <c r="D103" s="7">
         <v>66</v>
       </c>
@@ -2863,7 +2876,7 @@
         <v>132</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J103" s="3" t="s">
         <v>9</v>
@@ -2872,7 +2885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:11">
       <c r="D104" s="7">
         <v>67</v>
       </c>
@@ -2889,7 +2902,7 @@
         <v>133</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>9</v>
@@ -2898,7 +2911,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:11">
       <c r="D105" s="7">
         <v>68</v>
       </c>
@@ -2915,7 +2928,7 @@
         <v>134</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J105" s="3" t="s">
         <v>9</v>
@@ -2924,16 +2937,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:11">
       <c r="F110" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G110" s="11"/>
       <c r="H110" s="11"/>
       <c r="I110" s="11"/>
       <c r="J110" s="11"/>
     </row>
-    <row r="111" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:11">
       <c r="F111" s="10" t="s">
         <v>0</v>
       </c>
@@ -2941,16 +2954,16 @@
         <v>135</v>
       </c>
       <c r="H111" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="I111" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="J111" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="I111" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="J111" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="112" spans="4:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="4:11">
       <c r="F112" s="8">
         <v>1</v>
       </c>
@@ -2958,7 +2971,7 @@
         <v>140</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I112" s="7">
         <v>6</v>
@@ -2967,7 +2980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="6:10">
       <c r="F113" s="8">
         <v>2</v>
       </c>
@@ -2975,7 +2988,7 @@
         <v>146</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I113" s="7">
         <v>29</v>
@@ -2984,7 +2997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="6:10">
       <c r="F114" s="8">
         <v>3</v>
       </c>
@@ -2992,7 +3005,7 @@
         <v>143</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I114" s="7">
         <v>11</v>
@@ -3001,7 +3014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="6:10">
       <c r="F115" s="8">
         <v>4</v>
       </c>
@@ -3009,7 +3022,7 @@
         <v>144</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I115" s="7">
         <v>7</v>
@@ -3018,7 +3031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="6:10">
       <c r="F116" s="8">
         <v>5</v>
       </c>
@@ -3026,7 +3039,7 @@
         <v>139</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I116" s="7">
         <v>5</v>
@@ -3035,7 +3048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="6:10">
       <c r="F117" s="8">
         <v>6</v>
       </c>
@@ -3043,7 +3056,7 @@
         <v>137</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I117" s="7">
         <v>2</v>
@@ -3052,7 +3065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="6:10">
       <c r="F118" s="8">
         <v>7</v>
       </c>
@@ -3060,7 +3073,7 @@
         <v>145</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I118" s="7">
         <v>10</v>
@@ -3069,7 +3082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="6:10">
       <c r="F119" s="8">
         <v>8</v>
       </c>
@@ -3077,7 +3090,7 @@
         <v>148</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I119" s="7">
         <v>49</v>
@@ -3086,7 +3099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="6:10">
       <c r="F120" s="8">
         <v>9</v>
       </c>
@@ -3094,7 +3107,7 @@
         <v>150</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I120" s="7">
         <v>24</v>
@@ -3103,7 +3116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="6:10">
       <c r="F121" s="8">
         <v>10</v>
       </c>
@@ -3111,7 +3124,7 @@
         <v>142</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I121" s="7">
         <v>9</v>
@@ -3120,7 +3133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="6:10">
       <c r="F122" s="8">
         <v>11</v>
       </c>
@@ -3128,7 +3141,7 @@
         <v>149</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I122" s="7">
         <v>60</v>
@@ -3137,7 +3150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="6:10">
       <c r="F123" s="8">
         <v>12</v>
       </c>
@@ -3145,7 +3158,7 @@
         <v>138</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I123" s="7">
         <v>4</v>
@@ -3154,7 +3167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="6:10">
       <c r="F124" s="8">
         <v>13</v>
       </c>
@@ -3162,7 +3175,7 @@
         <v>147</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I124" s="7">
         <v>33</v>
@@ -3171,7 +3184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="6:10">
       <c r="F125" s="8">
         <v>14</v>
       </c>
@@ -3179,7 +3192,7 @@
         <v>141</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I125" s="7">
         <v>1</v>
@@ -3188,7 +3201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="6:10">
       <c r="F126" s="8">
         <v>15</v>
       </c>
@@ -3196,7 +3209,7 @@
         <v>151</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I126" s="7">
         <v>25</v>
@@ -3205,16 +3218,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="6:10">
       <c r="F131" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G131" s="11"/>
       <c r="H131" s="11"/>
       <c r="I131" s="11"/>
       <c r="J131" s="11"/>
     </row>
-    <row r="132" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="6:10">
       <c r="F132" s="2" t="s">
         <v>0</v>
       </c>
@@ -3228,15 +3241,15 @@
         <v>192</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="133" spans="6:10" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="133" spans="6:10">
       <c r="F133" s="9">
         <v>1</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H133" s="5">
         <v>45809</v>
@@ -3248,12 +3261,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="6:10">
       <c r="F134" s="9">
         <v>2</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H134" s="5">
         <v>45809</v>
@@ -3265,12 +3278,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="6:10">
       <c r="F135" s="9">
         <v>3</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H135" s="5">
         <v>45810</v>
@@ -3282,12 +3295,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="6:10">
       <c r="F136" s="9">
         <v>4</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H136" s="5">
         <v>45810</v>
@@ -3299,12 +3312,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="6:10">
       <c r="F137" s="9">
         <v>5</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H137" s="5">
         <v>45810</v>
@@ -3316,12 +3329,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="6:10">
       <c r="F138" s="9">
         <v>6</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H138" s="5">
         <v>45811</v>
@@ -3333,12 +3346,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="139" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="6:10">
       <c r="F139" s="9">
         <v>7</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H139" s="5">
         <v>45811</v>
@@ -3350,12 +3363,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="140" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="6:10">
       <c r="F140" s="9">
         <v>8</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H140" s="5">
         <v>45812</v>
@@ -3367,12 +3380,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="6:10">
       <c r="F141" s="9">
         <v>9</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H141" s="5">
         <v>45812</v>
@@ -3384,12 +3397,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="6:10">
       <c r="F142" s="9">
         <v>10</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H142" s="5">
         <v>45813</v>
@@ -3401,12 +3414,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="6:10">
       <c r="F143" s="9">
         <v>11</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H143" s="5">
         <v>45813</v>
@@ -3418,12 +3431,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="6:10">
       <c r="F144" s="9">
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H144" s="5">
         <v>45813</v>
@@ -3435,12 +3448,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="6:10">
       <c r="F145" s="9">
         <v>13</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H145" s="5">
         <v>45814</v>
@@ -3452,12 +3465,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="6:10">
       <c r="F146" s="9">
         <v>14</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H146" s="5">
         <v>45814</v>
@@ -3469,12 +3482,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="6:10">
       <c r="F147" s="9">
         <v>15</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H147" s="5">
         <v>45815</v>
@@ -3493,9 +3506,10 @@
     <mergeCell ref="F110:J110"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H38" r:id="rId1" xr:uid="{BB69F251-0421-4304-8604-D14CE97DF5AF}"/>
+    <hyperlink ref="H38" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3644,18 +3658,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3677,25 +3691,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0FA18E-0926-46C2-B252-4A5E541FB5A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="87289aac-3191-415d-94b6-004c2ae78a31"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F0B7D04-965F-41C4-A0F3-50622BBCC1F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0FA18E-0926-46C2-B252-4A5E541FB5A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="87289aac-3191-415d-94b6-004c2ae78a31"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>